--- a/Steuer-Vorlage-2026-free.xlsx
+++ b/Steuer-Vorlage-2026-free.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Nur für eigene Steuerzwecke. Keine Steuerberatung; bei Zweifeln Steuerberater oder Finanzamt fragen (§ 5 RDG). Angaben ohne Gewähr.</t>
+          <t>Nur für eigene Steuerzwecke. Keine Steuerberatung; bei Zweifeln Steuerberater oder Finanzamt fragen (§ 2, § 3 RDG). Angaben ohne Gewähr.</t>
         </is>
       </c>
     </row>

--- a/Steuer-Vorlage-2026-free.xlsx
+++ b/Steuer-Vorlage-2026-free.xlsx
@@ -2428,7 +2428,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>10.01.2026</t>
+          <t>12.01.2026</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -2496,12 +2496,12 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Gewerbesteuererklärung 2025 (bei Steuerberater: 28.02.2027)</t>
+          <t>Gewerbesteuererklärung 2025 (bei Steuerberater: 29.02.2028)</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -2530,7 +2530,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>10.01.2027</t>
+          <t>11.01.2027</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -2547,7 +2547,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>31.07.2027</t>
+          <t>02.08.2027</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
